--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,7 +782,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>季一冉</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -792,17 +792,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>天安@1104</t>
+          <t>天安@1164</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AP强化班</t>
+          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>全科</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1164</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>天安</t>
+          <t>天安@1146</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>季一冉</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -918,160 +918,160 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>天安@1104</t>
+          <t>天安@1123</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AP强化班</t>
+          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>全科</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>孙一渟</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1136</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>季一冉</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>天安</t>
+          <t>天安@1138</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>顾梓泷</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AMC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@949</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>AMC1对1</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>AMC12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>天安</t>
+          <t>天安@940</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1103,22 +1103,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>孙一渟</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1128,34 +1128,34 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>天安@1104</t>
+          <t>网络授课</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>AP强化班</t>
+          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>全科</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>天安@903</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1187,59 +1187,59 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>孙一渟</t>
+          <t>顾梓泷</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AMC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1120</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
+          <t>AMC1对1</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>AMC12</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>天安</t>
+          <t>天安@1146</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1271,49 +1271,49 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>天安@1104</t>
+          <t>天安@1146</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>AP强化班</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>全科</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>天安</t>
+          <t>天安@1136</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1355,64 +1355,64 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>天安@1104</t>
+          <t>天安@903</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>AP强化班</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>全科</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>孙一渟</t>
+          <t>季一冉</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1439,17 +1439,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1120</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1481,49 +1481,49 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>顾梓泷</t>
+          <t>任页霖</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AMC</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>天安@1120</t>
+          <t>国金@01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AMC1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>AMC12</t>
+          <t>基础数学</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>天安@946</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1565,7 +1565,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>季一冉</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1590,34 +1590,34 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>天安@1104</t>
+          <t>网络授课</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>AP强化班</t>
+          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>全科</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1649,7 +1649,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1664,657 +1664,153 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>天安@1104</t>
+          <t>天安</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>AP强化班</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>全科</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>季一冉</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>天安</t>
+          <t>网络授课</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>顾梓泷</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AMC</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>天安@1120</t>
+          <t>天安</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>AMC1对1</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>AMC12</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>天安@946</t>
+          <t>天安</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>高等数学</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>18:30:00</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>吴子墨</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>天安@949</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>A-LEVEL1对1</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>高等数学</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>10:20:00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>12:20:00</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>吴子墨</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>天安</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>A-LEVEL1对1</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>高等数学</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>13:50:00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>15:50:00</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>班课</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>AP微积分</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>天安@1104</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>AP强化班</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>全科</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>16:10:00</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>18:10:00</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>孙一渟</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AP微积分</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>网络授课</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
           <t>微积分BC</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>13:50:00</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>15:50:00</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>吴子墨</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>天安</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>A-LEVEL1对1</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>高等数学</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>18:30:00</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>吴子墨</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>天安@949</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>A-LEVEL1对1</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>高等数学</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>10:20:00</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>12:20:00</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>吴子墨</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>天安</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>A-LEVEL1对1</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>高等数学</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>13:50:00</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>15:50:00</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>班课</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AP微积分</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>天安@1104</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>AP强化班</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>全科</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>16:10:00</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>18:10:00</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>孙一渟</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AP微积分</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>网络授课</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>微积分BC</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>13:50:00</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>15:50:00</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>陈博扬</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AP微积分</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>天安</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>AP1对1</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>微积分BC</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>16:10:00</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>18:10:00</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>陈博扬</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AP微积分</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>天安</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>AP1对1</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>微积分BC</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>18:30:00</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>吴子墨</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>天安@949</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>A-LEVEL1对1</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>高等数学</t>
         </is>
       </c>
     </row>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1360,37 +1360,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>季一冉</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>网络授课</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
@@ -1402,79 +1402,79 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>季一冉</t>
+          <t>顾梓泷</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AMC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1120</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
+          <t>AMC1对1</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>AMC12</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>顾梓泷</t>
+          <t>任页霖</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AMC</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>天安@1120</t>
+          <t>国金@01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AMC1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>AMC12</t>
+          <t>基础数学</t>
         </is>
       </c>
     </row>
@@ -1486,17 +1486,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>任页霖</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>国金@01</t>
+          <t>天安@946</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1516,14 +1516,14 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>基础数学</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1538,27 +1538,27 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>季一冉</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>天安@946</t>
+          <t>网络授课</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
@@ -1570,17 +1570,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>季一冉</t>
+          <t>孙一渟</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1607,49 +1607,49 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>孙一渟</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1664,151 +1664,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>季一冉</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>天安</t>
+          <t>网络授课</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
-        <is>
-          <t>高等数学</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>13:50:00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>15:50:00</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>季一冉</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>AP微积分</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>网络授课</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>微积分BC</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>13:50:00</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>15:50:00</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>陈博扬</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>AP微积分</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>天安</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>AP1对1</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>微积分BC</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>16:10:00</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>18:10:00</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>陈博扬</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>AP微积分</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>天安</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>AP1对1</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
         <is>
           <t>微积分BC</t>
         </is>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1108,54 +1108,54 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>孙一渟</t>
+          <t>顾梓泷</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AMC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@903</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
+          <t>AMC1对1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>AMC12</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1120</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1192,54 +1192,54 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>顾梓泷</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AMC</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>天安@1120</t>
+          <t>天安@1146</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>AMC1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>AMC12</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1271,7 +1271,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>天安@1146</t>
+          <t>天安@1136</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1313,49 +1313,49 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>季一冉</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>天安@1136</t>
+          <t>网络授课</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1370,34 +1370,34 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>季一冉</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@946</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1439,91 +1439,91 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>任页霖</t>
+          <t>季一冉</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>国金@01</t>
+          <t>网络授课</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>基础数学</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>孙一渟</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>天安@946</t>
+          <t>网络授课</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1538,49 +1538,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>季一冉</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>孙一渟</t>
+          <t>季一冉</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1607,17 +1607,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>天安</t>
+          <t>天安@903</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1649,42 +1649,462 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>孙一渟</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>网络授课</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>杨涵予</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>天安@956</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>基础数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>天安@1138</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-11-14</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>天安@1138</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-11-14</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>13:50:00</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>15:50:00</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>季一冉</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>AP微积分</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>网络授课</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>天安@1138</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>孙一渟</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>网络授课</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-11-22</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>蔡伊洋</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AP计算机</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>天安@1129</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>高中北美计划卡 B计划VIP纯享-AP1对1</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>计算机科学</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-11-28</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>天安@903</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-11-28</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>季一冉</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>网络授课</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-11-29</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>蔡伊洋</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AP计算机</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>天安@1129</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>高中北美计划卡 B计划VIP纯享-AP1对1</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>计算机科学</t>
         </is>
       </c>
     </row>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1146</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1444,37 +1444,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>季一冉</t>
+          <t>修一然</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1122</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>统计学</t>
         </is>
       </c>
     </row>
@@ -1486,138 +1486,138 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>孙一渟</t>
+          <t>王允彤</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@923</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
+          <t>高中英联邦计划卡 A计划VIP纯享-AP1对1</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>统计学</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>孙一渟</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>天安</t>
+          <t>网络授课</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>季一冉</t>
+          <t>顾梓泷</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AMC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1120</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
+          <t>AMC1对1</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>AMC12</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1649,91 +1649,91 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>孙一渟</t>
+          <t>顾梓泷</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AMC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1120</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
+          <t>AMC1对1</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>AMC12</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>王允彤</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>天安@923</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>高中英联邦计划卡 A计划VIP纯享-AP1对1</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>基础数学</t>
+          <t>统计学</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>天安@1138</t>
+          <t>天安@903</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1775,64 +1775,64 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>顾梓泷</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AMC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>天安@1138</t>
+          <t>天安@1139</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>AMC1对1</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>AMC12</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>季一冉</t>
+          <t>孙一渟</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1859,49 +1859,49 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>王允彤</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>天安@1138</t>
+          <t>天安@923</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>高中英联邦计划卡 A计划VIP纯享-AP1对1</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>统计学</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1916,34 +1916,34 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>孙一渟</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@956</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>基础数学</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1958,151 +1958,529 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>蔡伊洋</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>天安@1129</t>
+          <t>天安@1138</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>高中北美计划卡 B计划VIP纯享-AP1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>计算机科学</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>王允彤</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@923</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>高中英联邦计划卡 A计划VIP纯享-AP1对1</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>统计学</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>季一冉</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1138</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>2026-11-14</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>季一冉</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>网络授课</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>王允彤</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AP统计学</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>天安@923</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 A计划VIP纯享-AP1对1</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>天安@1138</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>孙一渟</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>网络授课</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-11-22</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>蔡伊洋</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AP计算机</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>天安@1129</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>高中北美计划卡 B计划VIP纯享-AP1对1</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>计算机科学</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-11-22</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>王允彤</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AP统计学</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>天安@923</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 A计划VIP纯享-AP1对1</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-11-28</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>天安@903</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-11-28</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>王允彤</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AP统计学</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>天安@923</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 A计划VIP纯享-AP1对1</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-11-28</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>季一冉</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>网络授课</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 B计划VIP纯享-AP1对1</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>2026-11-29</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>10:20:00</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>12:20:00</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>蔡伊洋</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>AP计算机</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>天安@1129</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>高中北美计划卡 B计划VIP纯享-AP1对1</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>计算机科学</t>
         </is>
